--- a/artfynd/A 33800-2024 artfynd.xlsx
+++ b/artfynd/A 33800-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125984242</v>
       </c>
       <c r="B2" t="n">
-        <v>98248</v>
+        <v>98249</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33800-2024 artfynd.xlsx
+++ b/artfynd/A 33800-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125984242</v>
       </c>
       <c r="B2" t="n">
-        <v>98249</v>
+        <v>98251</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33800-2024 artfynd.xlsx
+++ b/artfynd/A 33800-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125984242</v>
       </c>
       <c r="B2" t="n">
-        <v>98251</v>
+        <v>98255</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33800-2024 artfynd.xlsx
+++ b/artfynd/A 33800-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125984242</v>
       </c>
       <c r="B2" t="n">
-        <v>98255</v>
+        <v>98256</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33800-2024 artfynd.xlsx
+++ b/artfynd/A 33800-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125984242</v>
       </c>
       <c r="B2" t="n">
-        <v>98256</v>
+        <v>98258</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33800-2024 artfynd.xlsx
+++ b/artfynd/A 33800-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125984242</v>
       </c>
       <c r="B2" t="n">
-        <v>98258</v>
+        <v>98260</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33800-2024 artfynd.xlsx
+++ b/artfynd/A 33800-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125984242</v>
       </c>
       <c r="B2" t="n">
-        <v>98260</v>
+        <v>98262</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33800-2024 artfynd.xlsx
+++ b/artfynd/A 33800-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125984242</v>
       </c>
       <c r="B2" t="n">
-        <v>98262</v>
+        <v>98266</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33800-2024 artfynd.xlsx
+++ b/artfynd/A 33800-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125984242</v>
       </c>
       <c r="B2" t="n">
-        <v>98266</v>
+        <v>98269</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33800-2024 artfynd.xlsx
+++ b/artfynd/A 33800-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125984242</v>
       </c>
       <c r="B2" t="n">
-        <v>98269</v>
+        <v>98278</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33800-2024 artfynd.xlsx
+++ b/artfynd/A 33800-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125984242</v>
+        <v>128260561</v>
       </c>
       <c r="B2" t="n">
-        <v>98278</v>
+        <v>91680</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219790</v>
+        <v>3215</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo, Upl</t>
+          <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>667892</v>
+        <v>667956</v>
       </c>
       <c r="R2" t="n">
-        <v>6691648</v>
+        <v>6691635</v>
       </c>
       <c r="S2" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -760,15 +760,311 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>126056868</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Östensbo-Bennebo, Upl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>668245</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6691768</v>
+      </c>
+      <c r="S3" t="n">
+        <v>15</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren, Shanti Wittmar</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>125855912</v>
+      </c>
+      <c r="B4" t="n">
+        <v>4781</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>102306</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Microbregma emarginatum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Östensbo-Bennebo, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>668276</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6691767</v>
+      </c>
+      <c r="S4" t="n">
+        <v>12</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Signe Propst</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Signe Propst</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>125984242</v>
+      </c>
+      <c r="B5" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Östensbo-Bennebo, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>667892</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6691648</v>
+      </c>
+      <c r="S5" t="n">
+        <v>12</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
           <t>Johanna Sollén Mattsson</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX5" t="inlineStr">
         <is>
           <t>Johanna Sollén Mattsson</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 33800-2024 artfynd.xlsx
+++ b/artfynd/A 33800-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128260561</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -871,6 +881,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126056868</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -968,6 +983,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125855912</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1065,8 +1085,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125984242</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>